--- a/results/ncbc_s17/m3/reference_peaks.xlsx
+++ b/results/ncbc_s17/m3/reference_peaks.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>step_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>peak_value</t>
         </is>
@@ -455,7 +443,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7305426479738373</v>
+        <v>0.7120478973922211</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +456,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8425142645326131</v>
+        <v>0.8211847894811546</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +469,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.144154520301309</v>
+        <v>1.115188583078491</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +482,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.149132213352397</v>
+        <v>1.120040258583982</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +495,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.168050094655599</v>
+        <v>1.138479206183306</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +508,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.145279796655943</v>
+        <v>1.116285371424147</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +521,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.185710314150681</v>
+        <v>1.155692331513955</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +534,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.208374703787545</v>
+        <v>1.177782939134696</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.179196949839151</v>
+        <v>1.149343862501451</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +560,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.17882627056939</v>
+        <v>1.148982567517</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.178971894568225</v>
+        <v>1.149124504832321</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +586,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.180361941829832</v>
+        <v>1.150479361024013</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +599,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.13793240398745</v>
+        <v>1.109123988696628</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +612,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.20427075472947</v>
+        <v>1.173782887521129</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +625,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.14113613196182</v>
+        <v>1.112246609633673</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +638,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.190502667566891</v>
+        <v>1.160363359527223</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +651,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.17097581317765</v>
+        <v>1.141330855882013</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +664,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.188808133762259</v>
+        <v>1.158711725312581</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +677,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.3756172471768802</v>
+        <v>0.3661079497799972</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +690,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.193031229728477</v>
+        <v>1.16282790745687</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +703,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.146193256285004</v>
+        <v>1.117175705492979</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +716,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.201715715477182</v>
+        <v>1.171292532806873</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +729,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.159802480903398</v>
+        <v>1.130440392779262</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +742,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.270225187656374</v>
+        <v>1.238067587968871</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.230469835974423</v>
+        <v>1.199318700886463</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +768,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.082409944795285</v>
+        <v>1.055007161382746</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +781,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.195321498073794</v>
+        <v>1.16506019432509</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +794,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.129724505871295</v>
+        <v>1.10112388546949</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +807,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.225730436739611</v>
+        <v>1.194699286442406</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +820,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.16662033175795</v>
+        <v>1.137085639814711</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +833,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.143691171214109</v>
+        <v>1.114736964347929</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +846,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.190304089386658</v>
+        <v>1.160169808642692</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +859,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.115215060169182</v>
+        <v>1.086981767506671</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +872,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.176244754226407</v>
+        <v>1.146466406018143</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +885,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.172590915710184</v>
+        <v>1.142905069742837</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +898,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.138541377073487</v>
+        <v>1.109717544742513</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +911,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.192845890093597</v>
+        <v>1.162647259964645</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +924,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.112448204191323</v>
+        <v>1.084284958515594</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +937,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.149582323894252</v>
+        <v>1.120478973922246</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +950,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.094854177422985</v>
+        <v>1.067136350146453</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.15993486635688</v>
+        <v>1.130569426702276</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +976,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.176310946953149</v>
+        <v>1.146530922979651</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +989,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.131220461495691</v>
+        <v>1.102581968799597</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1002,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.165270000132385</v>
+        <v>1.13576949379992</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1015,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.195136158438911</v>
+        <v>1.164879546832862</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1028,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.125845612084144</v>
+        <v>1.097343191525052</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1041,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.16639527648702</v>
+        <v>1.136866282145576</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1054,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.087837748388207</v>
+        <v>1.06029755222648</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1067,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.20010061294465</v>
+        <v>1.169718318946051</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1080,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.138739955253717</v>
+        <v>1.10991109562704</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1093,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.178018719303123</v>
+        <v>1.148195460586588</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1106,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.127182705164357</v>
+        <v>1.098646434147537</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1119,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.163893191416127</v>
+        <v>1.134427541000529</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1132,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.160848325985941</v>
+        <v>1.131459760771107</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1145,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.189575969392483</v>
+        <v>1.159460122066091</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1158,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.156969432198789</v>
+        <v>1.127679066826668</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.144353098481539</v>
+        <v>1.115382133963019</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1184,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.171849557170658</v>
+        <v>1.142182479773932</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1197,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.162264850338245</v>
+        <v>1.132840423747403</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1210,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.150350159524472</v>
+        <v>1.121227370675751</v>
       </c>
     </row>
     <row r="62">
@@ -1235,7 +1223,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.17222023644042</v>
+        <v>1.142543774758384</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1236,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.121145928485378</v>
+        <v>1.0927624872579</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1249,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.128056449157367</v>
+        <v>1.099498058039459</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1262,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.13229278366893</v>
+        <v>1.103627143576046</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1275,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.125117492089969</v>
+        <v>1.096633504948451</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1288,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.128493321153871</v>
+        <v>1.099923869985419</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1301,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.159670095449912</v>
+        <v>1.130311358856243</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1314,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.127010604074824</v>
+        <v>1.098478690047613</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1327,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.9083363120060368</v>
+        <v>0.885340456005884</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1340,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.176814011676397</v>
+        <v>1.147021251887121</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1353,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.128559513880615</v>
+        <v>1.099988386946928</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1366,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.237618650462687</v>
+        <v>1.206286532729455</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1379,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.164859605226576</v>
+        <v>1.135369488638562</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.115241537259886</v>
+        <v>1.087007574291281</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1405,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.202801276195772</v>
+        <v>1.172350610975625</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1418,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.180110409468208</v>
+        <v>1.150234196570278</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1431,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.194434515535433</v>
+        <v>1.164195667040865</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1444,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.13618491600143</v>
+        <v>1.107420740912786</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1457,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.170499225545102</v>
+        <v>1.14086633375915</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1470,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.158849305638296</v>
+        <v>1.12951134853353</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1483,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.142817427221097</v>
+        <v>1.113885340456006</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1496,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.147000807551266</v>
+        <v>1.117962812423386</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1509,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.13705865999444</v>
+        <v>1.108272364804707</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1522,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.179170472748454</v>
+        <v>1.149318055716848</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1535,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.122787508108609</v>
+        <v>1.094362507903328</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1548,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.18270516435654</v>
+        <v>1.152763261461438</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1561,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.13773382580722</v>
+        <v>1.108930437812101</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1574,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.17206137389624</v>
+        <v>1.142388934050766</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1587,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.1175318056052</v>
+        <v>1.089239861159499</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1600,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.133974078928207</v>
+        <v>1.105265874398379</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1613,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.11296450745992</v>
+        <v>1.084788190815365</v>
       </c>
     </row>
     <row r="93">
@@ -1638,7 +1626,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.18037518037518</v>
+        <v>1.150492264416315</v>
       </c>
     </row>
     <row r="94">
@@ -1651,7 +1639,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.184770377430928</v>
+        <v>1.154776190660525</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1652,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.129698028780598</v>
+        <v>1.101098078684886</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1665,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.13876643234444</v>
+        <v>1.109936902411669</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1678,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.104385930074004</v>
+        <v>1.076426792603776</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1691,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.138819386525792</v>
+        <v>1.109988515980835</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1704,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.172379098984604</v>
+        <v>1.142698615466006</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1717,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.132742894210802</v>
+        <v>1.104065858914327</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1730,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.160610032169665</v>
+        <v>1.131227499709674</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1743,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.120920873214451</v>
+        <v>1.092543129588769</v>
       </c>
     </row>
     <row r="103">
@@ -1768,7 +1756,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.093093450891616</v>
+        <v>1.065420198970309</v>
       </c>
     </row>
     <row r="104">
@@ -1781,7 +1769,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.164780173954486</v>
+        <v>1.135292068284752</v>
       </c>
     </row>
     <row r="105">
@@ -1794,7 +1782,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.106504097329795</v>
+        <v>1.078491335372078</v>
       </c>
     </row>
     <row r="106">
@@ -1807,7 +1795,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.204614956908535</v>
+        <v>1.174118375720977</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1808,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.16969167427883</v>
+        <v>1.140079226828733</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1821,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.137972119623496</v>
+        <v>1.109162698873534</v>
       </c>
     </row>
     <row r="109">
@@ -1846,7 +1834,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.112620305280841</v>
+        <v>1.084452702615504</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1847,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.168910600103261</v>
+        <v>1.139317926682925</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1860,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.142367316679253</v>
+        <v>1.113446625117753</v>
       </c>
     </row>
     <row r="112">
@@ -1885,7 +1873,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.182493347630962</v>
+        <v>1.152556807184609</v>
       </c>
     </row>
     <row r="113">
@@ -1898,7 +1886,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.168275149926526</v>
+        <v>1.138698563852437</v>
       </c>
     </row>
     <row r="114">
@@ -1911,7 +1899,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.133696069475868</v>
+        <v>1.104994903160023</v>
       </c>
     </row>
     <row r="115">
@@ -1924,7 +1912,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.122933132107444</v>
+        <v>1.094504445218648</v>
       </c>
     </row>
     <row r="116">
@@ -1937,7 +1925,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.169148893919536</v>
+        <v>1.139550187744358</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1938,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.117770099421479</v>
+        <v>1.089472122220935</v>
       </c>
     </row>
     <row r="118">
@@ -1963,7 +1951,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.118855660140064</v>
+        <v>1.090530200389682</v>
       </c>
     </row>
     <row r="119">
@@ -1976,7 +1964,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.148192276632644</v>
+        <v>1.119124117730551</v>
       </c>
     </row>
     <row r="120">
@@ -1989,7 +1977,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1.174801752783404</v>
+        <v>1.145059936257242</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +1990,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.153792181315117</v>
+        <v>1.124582252674228</v>
       </c>
     </row>
     <row r="122">
@@ -2015,7 +2003,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.167017488118409</v>
+        <v>1.137472741583766</v>
       </c>
     </row>
     <row r="123">
@@ -2028,7 +2016,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.063094907131601</v>
+        <v>1.036181112014346</v>
       </c>
     </row>
     <row r="124">
@@ -2041,7 +2029,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.05460899956314</v>
+        <v>1.027910037548883</v>
       </c>
     </row>
     <row r="125">
@@ -2054,7 +2042,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.6826191138117743</v>
+        <v>0.6653376172595775</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2055,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.5877252207527437</v>
+        <v>0.572846101240016</v>
       </c>
     </row>
     <row r="127">
@@ -2080,7 +2068,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.8654301865311096</v>
+        <v>0.8435205615556384</v>
       </c>
     </row>
     <row r="128">
@@ -2093,7 +2081,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.026927201239128</v>
+        <v>1.000929044245732</v>
       </c>
     </row>
     <row r="129">
@@ -2106,7 +2094,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.108079484226273</v>
+        <v>1.080026839055988</v>
       </c>
     </row>
     <row r="130">
@@ -2119,7 +2107,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.130121662231754</v>
+        <v>1.101510987238545</v>
       </c>
     </row>
     <row r="131">
@@ -2132,7 +2120,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.137548486172339</v>
+        <v>1.108749790319875</v>
       </c>
     </row>
     <row r="132">
@@ -2145,7 +2133,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.121556323391191</v>
+        <v>1.093162492419263</v>
       </c>
     </row>
     <row r="133">
@@ -2158,7 +2146,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1.143889749394337</v>
+        <v>1.114930515232454</v>
       </c>
     </row>
     <row r="134">
@@ -2171,7 +2159,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.161801501251043</v>
+        <v>1.13238880501684</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2172,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.12073553357957</v>
+        <v>1.092362482096543</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2185,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.110197651482055</v>
+        <v>1.082091381824282</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2198,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.102347194090313</v>
+        <v>1.074439670189293</v>
       </c>
     </row>
     <row r="138">
@@ -2223,7 +2211,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.134543336378201</v>
+        <v>1.105820720267361</v>
       </c>
     </row>
     <row r="139">
@@ -2236,7 +2224,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.076214305572104</v>
+        <v>1.048968373785468</v>
       </c>
     </row>
     <row r="140">
@@ -2249,7 +2237,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1.063531779128117</v>
+        <v>1.036606923960316</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2250,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.086315315673104</v>
+        <v>1.05881366211176</v>
       </c>
     </row>
     <row r="142">
@@ -2275,7 +2263,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1.065782331837378</v>
+        <v>1.038800500651621</v>
       </c>
     </row>
     <row r="143">
@@ -2288,7 +2276,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.115969657254061</v>
+        <v>1.087717260867882</v>
       </c>
     </row>
     <row r="144">
@@ -2301,7 +2289,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.003680315606909</v>
+        <v>0.978270687363696</v>
       </c>
     </row>
     <row r="145">
@@ -2314,7 +2302,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.091756357811404</v>
+        <v>1.064116956347824</v>
       </c>
     </row>
     <row r="146">
@@ -2327,7 +2315,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1.104465361346086</v>
+        <v>1.076504212957577</v>
       </c>
     </row>
     <row r="147">
@@ -2340,7 +2328,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.211048889947969</v>
+        <v>1.180389424379666</v>
       </c>
     </row>
     <row r="148">
@@ -2353,7 +2341,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1.184876285793729</v>
+        <v>1.154879417798951</v>
       </c>
     </row>
     <row r="149">
@@ -2366,7 +2354,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.157604882375525</v>
+        <v>1.128298429657157</v>
       </c>
     </row>
     <row r="150">
@@ -2379,7 +2367,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.180295749103089</v>
+        <v>1.150414844062504</v>
       </c>
     </row>
     <row r="151">
@@ -2392,7 +2380,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.091160623270715</v>
+        <v>1.063536303694242</v>
       </c>
     </row>
     <row r="152">
@@ -2405,7 +2393,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.180997392006566</v>
+        <v>1.151098723854501</v>
       </c>
     </row>
     <row r="153">
@@ -2418,7 +2406,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1.104928710433298</v>
+        <v>1.076955831688151</v>
       </c>
     </row>
     <row r="154">
@@ -2431,7 +2419,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.136065769093292</v>
+        <v>1.107304610382069</v>
       </c>
     </row>
     <row r="155">
@@ -2444,7 +2432,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.189271482849471</v>
+        <v>1.159163344043156</v>
       </c>
     </row>
     <row r="156">
@@ -2457,7 +2445,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.120086844857497</v>
+        <v>1.091730215873763</v>
       </c>
     </row>
     <row r="157">
@@ -2470,7 +2458,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.121278313938864</v>
+        <v>1.092891521180918</v>
       </c>
     </row>
     <row r="158">
@@ -2483,7 +2471,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1.115863748891277</v>
+        <v>1.087614033729473</v>
       </c>
     </row>
     <row r="159">
@@ -2496,7 +2484,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1.123926023008592</v>
+        <v>1.095472199641286</v>
       </c>
     </row>
     <row r="160">
@@ -2509,7 +2497,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.097634271946186</v>
+        <v>1.069846062529827</v>
       </c>
     </row>
     <row r="161">
@@ -2522,7 +2510,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.160490885261533</v>
+        <v>1.131111369178963</v>
       </c>
     </row>
     <row r="162">
@@ -2535,7 +2523,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.100480559196148</v>
+        <v>1.072620291874726</v>
       </c>
     </row>
     <row r="163">
@@ -2548,7 +2536,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.145332750837338</v>
+        <v>1.116336984993355</v>
       </c>
     </row>
     <row r="164">
@@ -2561,7 +2549,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.128983147331771</v>
+        <v>1.100401295500587</v>
       </c>
     </row>
     <row r="165">
@@ -2574,7 +2562,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1.124098124098115</v>
+        <v>1.095639943741201</v>
       </c>
     </row>
     <row r="166">
@@ -2587,7 +2575,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.103644571534476</v>
+        <v>1.07570420263487</v>
       </c>
     </row>
     <row r="167">
@@ -2600,7 +2588,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.14745091809312</v>
+        <v>1.118401527761649</v>
       </c>
     </row>
     <row r="168">
@@ -2613,7 +2601,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1.160159921627783</v>
+        <v>1.130788784371383</v>
       </c>
     </row>
     <row r="169">
@@ -2626,7 +2614,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1.052980658485246</v>
+        <v>1.026322920295746</v>
       </c>
     </row>
     <row r="170">
@@ -2639,7 +2627,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1.127910825158519</v>
+        <v>1.099356120724126</v>
       </c>
     </row>
     <row r="171">
@@ -2652,7 +2640,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1.093384698889286</v>
+        <v>1.06570407360095</v>
       </c>
     </row>
     <row r="172">
@@ -2665,7 +2653,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1.058037782808425</v>
+        <v>1.031252016155047</v>
       </c>
     </row>
     <row r="173">
@@ -2678,7 +2666,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.168288388471875</v>
+        <v>1.138711467244739</v>
       </c>
     </row>
     <row r="174">
@@ -2691,7 +2679,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1.118299641235421</v>
+        <v>1.089988257913005</v>
       </c>
     </row>
     <row r="175">
@@ -2704,7 +2692,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1.128903716059679</v>
+        <v>1.100323875146776</v>
       </c>
     </row>
     <row r="176">
@@ -2717,7 +2705,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.126864980075989</v>
+        <v>1.098336752732293</v>
       </c>
     </row>
     <row r="177">
@@ -2730,7 +2718,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.085428333134755</v>
+        <v>1.057949134827546</v>
       </c>
     </row>
     <row r="178">
@@ -2743,7 +2731,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1.099024319207805</v>
+        <v>1.071200918721532</v>
       </c>
     </row>
     <row r="179">
@@ -2756,7 +2744,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.161960363795226</v>
+        <v>1.132543645724461</v>
       </c>
     </row>
     <row r="180">
@@ -2769,7 +2757,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1.159233223453407</v>
+        <v>1.129885546910283</v>
       </c>
     </row>
     <row r="181">
@@ -2782,7 +2770,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1.14191720613739</v>
+        <v>1.113007909779481</v>
       </c>
     </row>
     <row r="182">
@@ -2795,7 +2783,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1.053165998120112</v>
+        <v>1.026503567787958</v>
       </c>
     </row>
     <row r="183">
@@ -2808,7 +2796,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1.124707097184162</v>
+        <v>1.096233499787094</v>
       </c>
     </row>
     <row r="184">
@@ -2821,7 +2809,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.106583528601877</v>
+        <v>1.07856875572588</v>
       </c>
     </row>
     <row r="185">
@@ -2834,7 +2822,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.199994704581861</v>
+        <v>1.169615091807636</v>
       </c>
     </row>
     <row r="186">
@@ -2847,7 +2835,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1.116485960522658</v>
+        <v>1.088220493167654</v>
       </c>
     </row>
     <row r="187">
@@ -2860,7 +2848,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1.141692150866463</v>
+        <v>1.11278855211035</v>
       </c>
     </row>
     <row r="188">
@@ -2873,7 +2861,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1.12355534373883</v>
+        <v>1.095110904656834</v>
       </c>
     </row>
     <row r="189">
@@ -2886,7 +2874,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1.087625931662612</v>
+        <v>1.060091097949634</v>
       </c>
     </row>
     <row r="190">
@@ -2899,7 +2887,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1.140209433787415</v>
+        <v>1.111343372172544</v>
       </c>
     </row>
     <row r="191">
@@ -2912,7 +2900,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1.152971391503502</v>
+        <v>1.123782242351514</v>
       </c>
     </row>
     <row r="192">
@@ -2925,7 +2913,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1.09133272436023</v>
+        <v>1.063704047794148</v>
       </c>
     </row>
     <row r="193">
@@ -2938,7 +2926,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1.134119702927042</v>
+        <v>1.105407811713699</v>
       </c>
     </row>
     <row r="194">
@@ -2951,7 +2939,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.7938228947403239</v>
+        <v>0.7737261125949992</v>
       </c>
     </row>
     <row r="195">
@@ -2964,7 +2952,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1.106517335875134</v>
+        <v>1.078504238764371</v>
       </c>
     </row>
     <row r="196">
@@ -2977,7 +2965,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1.100295219561275</v>
+        <v>1.072439644382508</v>
       </c>
     </row>
     <row r="197">
@@ -2990,7 +2978,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.122469783020242</v>
+        <v>1.094052826488084</v>
       </c>
     </row>
     <row r="198">
@@ -3003,7 +2991,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1.144842924659438</v>
+        <v>1.115859559478187</v>
       </c>
     </row>
     <row r="199">
@@ -3016,7 +3004,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1.141586242503674</v>
+        <v>1.112685324971935</v>
       </c>
     </row>
     <row r="200">
@@ -3029,7 +3017,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1.101142486463587</v>
+        <v>1.073265461489826</v>
       </c>
     </row>
     <row r="201">
@@ -3042,7 +3030,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1.091650449448615</v>
+        <v>1.064013729209409</v>
       </c>
     </row>
     <row r="202">
@@ -3055,7 +3043,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1.14637859591988</v>
+        <v>1.1173563529852</v>
       </c>
     </row>
     <row r="203">
@@ -3068,7 +3056,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.127910825158532</v>
+        <v>1.099356120724138</v>
       </c>
     </row>
     <row r="204">
@@ -3081,7 +3069,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1.105497967883271</v>
+        <v>1.077510677557113</v>
       </c>
     </row>
     <row r="205">
@@ -3094,7 +3082,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1.159047883818526</v>
+        <v>1.129704899418057</v>
       </c>
     </row>
     <row r="206">
@@ -3107,7 +3095,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1.148059891179157</v>
+        <v>1.118995083807533</v>
       </c>
     </row>
     <row r="207">
@@ -3120,7 +3108,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1.122350636112104</v>
+        <v>1.093936695957367</v>
       </c>
     </row>
     <row r="208">
@@ -3133,7 +3121,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1.153792181315117</v>
+        <v>1.124582252674228</v>
       </c>
     </row>
     <row r="209">
@@ -3146,7 +3134,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.129446496418973</v>
+        <v>1.100852914231151</v>
       </c>
     </row>
     <row r="210">
@@ -3159,7 +3147,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1.134225611289831</v>
+        <v>1.105511038852114</v>
       </c>
     </row>
     <row r="211">
@@ -3172,7 +3160,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1.111720084197148</v>
+        <v>1.083575271938993</v>
       </c>
     </row>
     <row r="212">
@@ -3185,7 +3173,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.166262891033533</v>
+        <v>1.136737248222558</v>
       </c>
     </row>
     <row r="213">
@@ -3198,7 +3186,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1.043488621470255</v>
+        <v>1.017071188015312</v>
       </c>
     </row>
     <row r="214">
@@ -3211,7 +3199,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1.171267061175318</v>
+        <v>1.141614730512652</v>
       </c>
     </row>
     <row r="215">
@@ -3224,7 +3212,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1.111137588201808</v>
+        <v>1.083007522677712</v>
       </c>
     </row>
     <row r="216">
@@ -3237,7 +3225,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1.145041502839668</v>
+        <v>1.116053110362714</v>
       </c>
     </row>
     <row r="217">
@@ -3250,7 +3238,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1.097356262493877</v>
+        <v>1.069575091291501</v>
       </c>
     </row>
     <row r="218">
@@ -3263,7 +3251,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1.121291552484213</v>
+        <v>1.09290442457322</v>
       </c>
     </row>
     <row r="219">
@@ -3276,7 +3264,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1.173716192064816</v>
+        <v>1.144001858088491</v>
       </c>
     </row>
     <row r="220">
@@ -3289,7 +3277,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1.154109906403503</v>
+        <v>1.12489193408949</v>
       </c>
     </row>
     <row r="221">
@@ -3302,7 +3290,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1.152349179872116</v>
+        <v>1.123175782913328</v>
       </c>
     </row>
     <row r="222">
@@ -3315,7 +3303,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1.143042482491977</v>
+        <v>1.114104698125091</v>
       </c>
     </row>
     <row r="223">
@@ -3328,7 +3316,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.07780293101393</v>
+        <v>1.050516780861679</v>
       </c>
     </row>
     <row r="224">
@@ -3341,7 +3329,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1.155235182758118</v>
+        <v>1.125988722435128</v>
       </c>
     </row>
     <row r="225">
@@ -3354,7 +3342,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1.101221917735679</v>
+        <v>1.073342881843637</v>
       </c>
     </row>
     <row r="226">
@@ -3367,7 +3355,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.131339608403778</v>
+        <v>1.102698099330265</v>
       </c>
     </row>
     <row r="227">
@@ -3380,7 +3368,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1.131710287673621</v>
+        <v>1.103059394314795</v>
       </c>
     </row>
     <row r="228">
@@ -3393,7 +3381,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1.104068204985608</v>
+        <v>1.076117111188504</v>
       </c>
     </row>
     <row r="229">
@@ -3406,7 +3394,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1.117968677601705</v>
+        <v>1.089665673105459</v>
       </c>
     </row>
     <row r="230">
@@ -3419,7 +3407,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1.102519295179845</v>
+        <v>1.074607414289217</v>
       </c>
     </row>
     <row r="231">
@@ -3432,7 +3420,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1.103287130810066</v>
+        <v>1.075355811042723</v>
       </c>
     </row>
     <row r="232">
@@ -3445,7 +3433,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1.119941220858627</v>
+        <v>1.091588278558408</v>
       </c>
     </row>
     <row r="233">
@@ -3458,7 +3446,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1.145041502839715</v>
+        <v>1.11605311036276</v>
       </c>
     </row>
     <row r="234">
@@ -3471,7 +3459,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1.123290572831773</v>
+        <v>1.094852836810716</v>
       </c>
     </row>
     <row r="235">
@@ -3484,7 +3472,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1.121053258667938</v>
+        <v>1.092672163511787</v>
       </c>
     </row>
     <row r="236">
@@ -3497,7 +3485,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1.112858599097131</v>
+        <v>1.084684963676951</v>
       </c>
     </row>
     <row r="237">
@@ -3510,7 +3498,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1.151051802427988</v>
+        <v>1.121911250467786</v>
       </c>
     </row>
     <row r="238">
@@ -3523,7 +3511,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1.145623998834982</v>
+        <v>1.11662085962397</v>
       </c>
     </row>
     <row r="239">
@@ -3536,7 +3524,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1.125991236082979</v>
+        <v>1.097485128840372</v>
       </c>
     </row>
     <row r="240">
@@ -3549,7 +3537,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1.096945867588069</v>
+        <v>1.069175086130144</v>
       </c>
     </row>
     <row r="241">
@@ -3562,7 +3550,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1.145385705018733</v>
+        <v>1.116388598562562</v>
       </c>
     </row>
     <row r="242">
@@ -3575,7 +3563,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1.084170671326625</v>
+        <v>1.056723312558863</v>
       </c>
     </row>
     <row r="243">
@@ -3588,7 +3576,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1.156294266386009</v>
+        <v>1.127020993819275</v>
       </c>
     </row>
     <row r="244">
@@ -3601,7 +3589,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1.082926248063804</v>
+        <v>1.055510393682442</v>
       </c>
     </row>
     <row r="245">
@@ -3614,7 +3602,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1.118829183049367</v>
+        <v>1.090504393605079</v>
       </c>
     </row>
     <row r="246">
@@ -3627,7 +3615,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1.092140275626471</v>
+        <v>1.064491154724535</v>
       </c>
     </row>
     <row r="247">
@@ -3640,7 +3628,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1.07855752809881</v>
+        <v>1.05125227422289</v>
       </c>
     </row>
     <row r="248">
@@ -3653,7 +3641,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1.031613646292566</v>
+        <v>1.005496845120602</v>
       </c>
     </row>
     <row r="249">
@@ -3666,7 +3654,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1.0072414843057</v>
+        <v>0.9817416998928978</v>
       </c>
     </row>
     <row r="250">
@@ -3679,7 +3667,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>0.9774812343619683</v>
+        <v>0.9527348739983742</v>
       </c>
     </row>
   </sheetData>
